--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-02-2026.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>£10.48</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>£12.15</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>£15.26</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>£15.86</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>£19.75</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>£22.06</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>£22.11</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1232,38 +1232,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_INTERNET_DISCONNECTED
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7b383f3d5
-	0x7ff7b383f430
-	0x7ff7b35e10bd
-	0x7ff7b35ddbe4
-	0x7ff7b35ce071
-	0x7ff7b35cff5f
-	0x7ff7b35ce611
-	0x7ff7b35cdddb
-	0x7ff7b35cda91
-	0x7ff7b35cb6c1
-	0x7ff7b35cbe22
-	0x7ff7b35e5366
-	0x7ff7b368ab34
-	0x7ff7b366589a
-	0x7ff7b3689d08
-	0x7ff7b362cb0c
-	0x7ff7b362da53
-	0x7ff7b3b1b470
-	0x7ff7b3b1586d
-	0x7ff7b3b3621a
-	0x7ff7b385b235
-	0x7ff7b3863a5c
-	0x7ff7b3848844
-	0x7ff7b38489f6
-	0x7ff7b382eb87
-	0x7fff13e1e8d7
-	0x7fff15aec40c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2220,17 +2189,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£35.95</t>
+          <t>£34.95</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£35.95</t>
+          <t>£34.95</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£35.95</t>
+          <t>£34.95</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2362,7 +2331,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Read timed out. (read timeout=30)</t>
+          <t>£72.69</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
